--- a/artfynd/A 64018-2020 artfynd.xlsx
+++ b/artfynd/A 64018-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64018-2020 artfynd.xlsx
+++ b/artfynd/A 64018-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY161"/>
+  <dimension ref="A1:AY158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5782,7 +5782,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>102647335</v>
+        <v>102648168</v>
       </c>
       <c r="B47" t="n">
         <v>78569</v>
@@ -5823,10 +5823,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563053.6111565963</v>
+        <v>563135.4293783343</v>
       </c>
       <c r="R47" t="n">
-        <v>6981086.190319465</v>
+        <v>6981098.242142129</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5895,10 +5895,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>102648168</v>
+        <v>102649707</v>
       </c>
       <c r="B48" t="n">
-        <v>78569</v>
+        <v>56411</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5911,35 +5911,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563135.4293783343</v>
+        <v>563265.5150961125</v>
       </c>
       <c r="R48" t="n">
-        <v>6981098.242142129</v>
+        <v>6981159.938017352</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5982,6 +5984,11 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6008,10 +6015,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>102649707</v>
+        <v>102653889</v>
       </c>
       <c r="B49" t="n">
-        <v>56411</v>
+        <v>78569</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6024,37 +6031,35 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563265.5150961125</v>
+        <v>562820.2830122286</v>
       </c>
       <c r="R49" t="n">
-        <v>6981159.938017352</v>
+        <v>6981651.102846227</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6097,11 +6102,6 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6128,10 +6128,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>102653889</v>
+        <v>102654618</v>
       </c>
       <c r="B50" t="n">
-        <v>78569</v>
+        <v>78596</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6140,25 +6140,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562820.2830122286</v>
+        <v>562876.2178038324</v>
       </c>
       <c r="R50" t="n">
-        <v>6981651.102846227</v>
+        <v>6981515.639529922</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6241,10 +6241,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>102654618</v>
+        <v>102650288</v>
       </c>
       <c r="B51" t="n">
-        <v>78596</v>
+        <v>98431</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6257,35 +6257,36 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>222771</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562876.2178038324</v>
+        <v>563192.7259443149</v>
       </c>
       <c r="R51" t="n">
-        <v>6981515.639529922</v>
+        <v>6981293.718333599</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6354,10 +6355,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>102650288</v>
+        <v>102652546</v>
       </c>
       <c r="B52" t="n">
-        <v>98431</v>
+        <v>77506</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6366,40 +6367,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222771</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>563192.7259443149</v>
+        <v>562920.0495905916</v>
       </c>
       <c r="R52" t="n">
-        <v>6981293.718333599</v>
+        <v>6981913.347864792</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>102652546</v>
+        <v>102653195</v>
       </c>
       <c r="B53" t="n">
-        <v>77506</v>
+        <v>96354</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6480,39 +6480,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562920.0495905916</v>
+        <v>562881.136305872</v>
       </c>
       <c r="R53" t="n">
-        <v>6981913.347864792</v>
+        <v>6981827.949521014</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6581,10 +6582,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>102653195</v>
+        <v>102652521</v>
       </c>
       <c r="B54" t="n">
-        <v>96354</v>
+        <v>78603</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6597,36 +6598,35 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562881.136305872</v>
+        <v>562920.0495905916</v>
       </c>
       <c r="R54" t="n">
-        <v>6981827.949521014</v>
+        <v>6981913.347864792</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6695,10 +6695,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>102652521</v>
+        <v>102653792</v>
       </c>
       <c r="B55" t="n">
-        <v>78603</v>
+        <v>78569</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6707,25 +6707,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562920.0495905916</v>
+        <v>562842.5979505827</v>
       </c>
       <c r="R55" t="n">
-        <v>6981913.347864792</v>
+        <v>6981699.320597377</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6808,7 +6808,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>102653792</v>
+        <v>102651081</v>
       </c>
       <c r="B56" t="n">
         <v>78569</v>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562842.5979505827</v>
+        <v>562913.7784049902</v>
       </c>
       <c r="R56" t="n">
-        <v>6981699.320597377</v>
+        <v>6981553.230263358</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6921,10 +6921,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>102651081</v>
+        <v>102651447</v>
       </c>
       <c r="B57" t="n">
-        <v>78569</v>
+        <v>56540</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6937,35 +6937,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562913.7784049902</v>
+        <v>562936.3455900083</v>
       </c>
       <c r="R57" t="n">
-        <v>6981553.230263358</v>
+        <v>6981635.589887266</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7034,10 +7040,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102651447</v>
+        <v>102654664</v>
       </c>
       <c r="B58" t="n">
-        <v>56540</v>
+        <v>78569</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7050,41 +7056,35 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562936.3455900083</v>
+        <v>562842.4413773438</v>
       </c>
       <c r="R58" t="n">
-        <v>6981635.589887266</v>
+        <v>6981494.507114689</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7153,10 +7153,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>102654664</v>
+        <v>102653819</v>
       </c>
       <c r="B59" t="n">
-        <v>78569</v>
+        <v>98520</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7165,39 +7165,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562842.4413773438</v>
+        <v>562824.9265127952</v>
       </c>
       <c r="R59" t="n">
-        <v>6981494.507114689</v>
+        <v>6981693.973900065</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7266,10 +7267,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>102653819</v>
+        <v>102653863</v>
       </c>
       <c r="B60" t="n">
-        <v>98520</v>
+        <v>78569</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7278,40 +7279,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562824.9265127952</v>
+        <v>562817.8824391873</v>
       </c>
       <c r="R60" t="n">
-        <v>6981693.973900065</v>
+        <v>6981681.094844135</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7380,10 +7380,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>102653863</v>
+        <v>102654600</v>
       </c>
       <c r="B61" t="n">
-        <v>78569</v>
+        <v>96367</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7392,39 +7392,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562817.8824391873</v>
+        <v>562876.2178038324</v>
       </c>
       <c r="R61" t="n">
-        <v>6981681.094844135</v>
+        <v>6981515.639529922</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7493,10 +7494,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102654600</v>
+        <v>102650106</v>
       </c>
       <c r="B62" t="n">
-        <v>96367</v>
+        <v>78569</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7505,40 +7506,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562876.2178038324</v>
+        <v>563285.2454500609</v>
       </c>
       <c r="R62" t="n">
-        <v>6981515.639529922</v>
+        <v>6981247.262254305</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7607,7 +7607,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102650106</v>
+        <v>102650590</v>
       </c>
       <c r="B63" t="n">
         <v>78569</v>
@@ -7648,10 +7648,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>563285.2454500609</v>
+        <v>563140.351105189</v>
       </c>
       <c r="R63" t="n">
-        <v>6981247.262254305</v>
+        <v>6981409.227963313</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7720,7 +7720,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102650590</v>
+        <v>102655652</v>
       </c>
       <c r="B64" t="n">
         <v>78569</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>563140.351105189</v>
+        <v>562908.5115978073</v>
       </c>
       <c r="R64" t="n">
-        <v>6981409.227963313</v>
+        <v>6981235.424969721</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7833,10 +7833,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102655652</v>
+        <v>102649552</v>
       </c>
       <c r="B65" t="n">
-        <v>78569</v>
+        <v>89356</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7845,25 +7845,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7874,10 +7874,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562908.5115978073</v>
+        <v>563263.1313975481</v>
       </c>
       <c r="R65" t="n">
-        <v>6981235.424969721</v>
+        <v>6981094.7978853</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7946,10 +7946,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>102649552</v>
+        <v>102648120</v>
       </c>
       <c r="B66" t="n">
-        <v>89356</v>
+        <v>78596</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7962,21 +7962,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563263.1313975481</v>
+        <v>563133.5384192481</v>
       </c>
       <c r="R66" t="n">
-        <v>6981094.7978853</v>
+        <v>6981078.176452862</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102648120</v>
+        <v>102648592</v>
       </c>
       <c r="B67" t="n">
-        <v>78596</v>
+        <v>96334</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8071,39 +8071,40 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563133.5384192481</v>
+        <v>563167.2909812659</v>
       </c>
       <c r="R67" t="n">
-        <v>6981078.176452862</v>
+        <v>6981100.679614399</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8172,10 +8173,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102648592</v>
+        <v>102652229</v>
       </c>
       <c r="B68" t="n">
-        <v>96334</v>
+        <v>77506</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8184,40 +8185,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>563167.2909812659</v>
+        <v>562967.2264359661</v>
       </c>
       <c r="R68" t="n">
-        <v>6981100.679614399</v>
+        <v>6981901.060544543</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8286,10 +8286,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102652229</v>
+        <v>102651331</v>
       </c>
       <c r="B69" t="n">
-        <v>77506</v>
+        <v>78596</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8298,25 +8298,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562967.2264359661</v>
+        <v>562932.3960144327</v>
       </c>
       <c r="R69" t="n">
-        <v>6981901.060544543</v>
+        <v>6981580.442555131</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8399,10 +8399,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102651331</v>
+        <v>102653615</v>
       </c>
       <c r="B70" t="n">
-        <v>78596</v>
+        <v>96354</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8415,35 +8415,36 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562932.3960144327</v>
+        <v>562836.5174969678</v>
       </c>
       <c r="R70" t="n">
-        <v>6981580.442555131</v>
+        <v>6981731.061723021</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8512,10 +8513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>102653615</v>
+        <v>102651568</v>
       </c>
       <c r="B71" t="n">
-        <v>96354</v>
+        <v>78602</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8528,36 +8529,35 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562836.5174969678</v>
+        <v>562952.4494075913</v>
       </c>
       <c r="R71" t="n">
-        <v>6981731.061723021</v>
+        <v>6981627.708260817</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8626,10 +8626,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>102651568</v>
+        <v>102651851</v>
       </c>
       <c r="B72" t="n">
-        <v>78602</v>
+        <v>89392</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8638,25 +8638,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8667,10 +8667,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562952.4494075913</v>
+        <v>562960.5680954895</v>
       </c>
       <c r="R72" t="n">
-        <v>6981627.708260817</v>
+        <v>6981702.960655795</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8739,10 +8739,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102651851</v>
+        <v>102649840</v>
       </c>
       <c r="B73" t="n">
-        <v>89392</v>
+        <v>89406</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8755,21 +8755,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8780,10 +8780,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562960.5680954895</v>
+        <v>563269.5189855509</v>
       </c>
       <c r="R73" t="n">
-        <v>6981702.960655795</v>
+        <v>6981165.022823947</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8852,10 +8852,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102649840</v>
+        <v>102655527</v>
       </c>
       <c r="B74" t="n">
-        <v>89406</v>
+        <v>96334</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8864,39 +8864,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>563269.5189855509</v>
+        <v>562875.2576188016</v>
       </c>
       <c r="R74" t="n">
-        <v>6981165.022823947</v>
+        <v>6981257.998329353</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8965,10 +8966,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102655527</v>
+        <v>102649856</v>
       </c>
       <c r="B75" t="n">
-        <v>96334</v>
+        <v>78569</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8977,40 +8978,39 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562875.2576188016</v>
+        <v>563282.2742174083</v>
       </c>
       <c r="R75" t="n">
-        <v>6981257.998329353</v>
+        <v>6981188.940342984</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9079,7 +9079,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102649856</v>
+        <v>102654163</v>
       </c>
       <c r="B76" t="n">
         <v>78569</v>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563282.2742174083</v>
+        <v>562858.6316109765</v>
       </c>
       <c r="R76" t="n">
-        <v>6981188.940342984</v>
+        <v>6981647.745394537</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9192,7 +9192,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102654163</v>
+        <v>102654597</v>
       </c>
       <c r="B77" t="n">
         <v>78569</v>
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562858.6316109765</v>
+        <v>562876.2178038324</v>
       </c>
       <c r="R77" t="n">
-        <v>6981647.745394537</v>
+        <v>6981515.639529922</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9305,7 +9305,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102654597</v>
+        <v>102650387</v>
       </c>
       <c r="B78" t="n">
         <v>78569</v>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562876.2178038324</v>
+        <v>563199.2229863395</v>
       </c>
       <c r="R78" t="n">
-        <v>6981515.639529922</v>
+        <v>6981334.809999548</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9418,10 +9418,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>102650387</v>
+        <v>102653268</v>
       </c>
       <c r="B79" t="n">
-        <v>78569</v>
+        <v>94121</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9434,35 +9434,36 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563199.2229863395</v>
+        <v>562879.6915559154</v>
       </c>
       <c r="R79" t="n">
-        <v>6981334.809999548</v>
+        <v>6981784.686649747</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9531,10 +9532,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>102653268</v>
+        <v>102652086</v>
       </c>
       <c r="B80" t="n">
-        <v>94121</v>
+        <v>78569</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9547,36 +9548,35 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562879.6915559154</v>
+        <v>562983.1042525045</v>
       </c>
       <c r="R80" t="n">
-        <v>6981784.686649747</v>
+        <v>6981834.012639266</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9645,10 +9645,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>102652086</v>
+        <v>102651427</v>
       </c>
       <c r="B81" t="n">
-        <v>78569</v>
+        <v>89673</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9661,21 +9661,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>562983.1042525045</v>
+        <v>562936.3455900083</v>
       </c>
       <c r="R81" t="n">
-        <v>6981834.012639266</v>
+        <v>6981635.589887266</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9758,10 +9758,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>102651427</v>
+        <v>102650344</v>
       </c>
       <c r="B82" t="n">
-        <v>89673</v>
+        <v>78569</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9774,21 +9774,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>562936.3455900083</v>
+        <v>563172.3781646057</v>
       </c>
       <c r="R82" t="n">
-        <v>6981635.589887266</v>
+        <v>6981308.800332777</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9871,10 +9871,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>102650344</v>
+        <v>102650199</v>
       </c>
       <c r="B83" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9887,21 +9887,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9912,10 +9912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563172.3781646057</v>
+        <v>563222.8423920701</v>
       </c>
       <c r="R83" t="n">
-        <v>6981308.800332777</v>
+        <v>6981292.025878593</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9984,10 +9984,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>102650199</v>
+        <v>102651546</v>
       </c>
       <c r="B84" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10000,21 +10000,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563222.8423920701</v>
+        <v>562952.4494075913</v>
       </c>
       <c r="R84" t="n">
-        <v>6981292.025878593</v>
+        <v>6981627.708260817</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10071,6 +10071,11 @@
       <c r="AB84" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10097,7 +10102,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>102651546</v>
+        <v>102652517</v>
       </c>
       <c r="B85" t="n">
         <v>78569</v>
@@ -10138,10 +10143,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>562952.4494075913</v>
+        <v>562920.0495905916</v>
       </c>
       <c r="R85" t="n">
-        <v>6981627.708260817</v>
+        <v>6981913.347864792</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10184,11 +10189,6 @@
       <c r="AB85" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10215,10 +10215,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>102652517</v>
+        <v>102652456</v>
       </c>
       <c r="B86" t="n">
-        <v>78569</v>
+        <v>78570</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10231,21 +10231,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10256,10 +10256,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>562920.0495905916</v>
+        <v>562929.2747865021</v>
       </c>
       <c r="R86" t="n">
-        <v>6981913.347864792</v>
+        <v>6981907.609637787</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10328,10 +10328,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>102652456</v>
+        <v>102653114</v>
       </c>
       <c r="B87" t="n">
-        <v>78570</v>
+        <v>78569</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10344,21 +10344,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10369,10 +10369,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>562929.2747865021</v>
+        <v>562889.9845215318</v>
       </c>
       <c r="R87" t="n">
-        <v>6981907.609637787</v>
+        <v>6981841.773144181</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>102653114</v>
+        <v>102652529</v>
       </c>
       <c r="B88" t="n">
-        <v>78569</v>
+        <v>78533</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10453,25 +10453,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562889.9845215318</v>
+        <v>562920.0495905916</v>
       </c>
       <c r="R88" t="n">
-        <v>6981841.773144181</v>
+        <v>6981913.347864792</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10554,10 +10554,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>102652529</v>
+        <v>102654839</v>
       </c>
       <c r="B89" t="n">
-        <v>78533</v>
+        <v>78569</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10566,25 +10566,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10595,10 +10595,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>562920.0495905916</v>
+        <v>562835.2392993235</v>
       </c>
       <c r="R89" t="n">
-        <v>6981913.347864792</v>
+        <v>6981442.481044792</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10667,7 +10667,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>102654839</v>
+        <v>102654719</v>
       </c>
       <c r="B90" t="n">
         <v>78569</v>
@@ -10708,10 +10708,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562835.2392993235</v>
+        <v>562836.387020988</v>
       </c>
       <c r="R90" t="n">
-        <v>6981442.481044792</v>
+        <v>6981477.549958516</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10780,10 +10780,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>102654719</v>
+        <v>102655098</v>
       </c>
       <c r="B91" t="n">
-        <v>78569</v>
+        <v>89392</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10796,21 +10796,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10821,10 +10821,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562836.387020988</v>
+        <v>562804.072420466</v>
       </c>
       <c r="R91" t="n">
-        <v>6981477.549958516</v>
+        <v>6981356.765708966</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10893,10 +10893,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>102655098</v>
+        <v>102648049</v>
       </c>
       <c r="B92" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10909,21 +10909,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562804.072420466</v>
+        <v>563131.7157314018</v>
       </c>
       <c r="R92" t="n">
-        <v>6981356.765708966</v>
+        <v>6981078.141187244</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -11006,10 +11006,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>102648049</v>
+        <v>102654101</v>
       </c>
       <c r="B93" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11022,21 +11022,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>563131.7157314018</v>
+        <v>562808.5690170951</v>
       </c>
       <c r="R93" t="n">
-        <v>6981078.141187244</v>
+        <v>6981644.05038748</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11119,10 +11119,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>102654101</v>
+        <v>102649331</v>
       </c>
       <c r="B94" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11135,21 +11135,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11160,10 +11160,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562808.5690170951</v>
+        <v>563253.3241659806</v>
       </c>
       <c r="R94" t="n">
-        <v>6981644.05038748</v>
+        <v>6981106.898312436</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11232,10 +11232,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>102649331</v>
+        <v>102647690</v>
       </c>
       <c r="B95" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11248,21 +11248,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>563253.3241659806</v>
+        <v>563079.9309635329</v>
       </c>
       <c r="R95" t="n">
-        <v>6981106.898312436</v>
+        <v>6981139.502584225</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11345,7 +11345,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>102647690</v>
+        <v>102652189</v>
       </c>
       <c r="B96" t="n">
         <v>78569</v>
@@ -11386,10 +11386,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>563079.9309635329</v>
+        <v>562967.6051341762</v>
       </c>
       <c r="R96" t="n">
-        <v>6981139.502584225</v>
+        <v>6981857.833748336</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11432,6 +11432,11 @@
       <c r="AB96" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11458,7 +11463,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>102652189</v>
+        <v>102652462</v>
       </c>
       <c r="B97" t="n">
         <v>78569</v>
@@ -11499,10 +11504,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562967.6051341762</v>
+        <v>562929.2747865021</v>
       </c>
       <c r="R97" t="n">
-        <v>6981857.833748336</v>
+        <v>6981907.609637787</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11545,11 +11550,6 @@
       <c r="AB97" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11576,10 +11576,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>102652462</v>
+        <v>102653116</v>
       </c>
       <c r="B98" t="n">
-        <v>78569</v>
+        <v>96251</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11588,39 +11588,40 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562929.2747865021</v>
+        <v>562889.9845215318</v>
       </c>
       <c r="R98" t="n">
-        <v>6981907.609637787</v>
+        <v>6981841.773144181</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11689,10 +11690,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>102653116</v>
+        <v>102654565</v>
       </c>
       <c r="B99" t="n">
-        <v>96251</v>
+        <v>78569</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11701,40 +11702,39 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562889.9845215318</v>
+        <v>562884.1122715238</v>
       </c>
       <c r="R99" t="n">
-        <v>6981841.773144181</v>
+        <v>6981508.054198722</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11803,7 +11803,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>102654565</v>
+        <v>102654007</v>
       </c>
       <c r="B100" t="n">
         <v>78569</v>
@@ -11844,10 +11844,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562884.1122715238</v>
+        <v>562808.2799592296</v>
       </c>
       <c r="R100" t="n">
-        <v>6981508.054198722</v>
+        <v>6981659.063998986</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11916,7 +11916,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>102654007</v>
+        <v>102653847</v>
       </c>
       <c r="B101" t="n">
         <v>78569</v>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562808.2799592296</v>
+        <v>562856.3529100325</v>
       </c>
       <c r="R101" t="n">
-        <v>6981659.063998986</v>
+        <v>6981718.700592224</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -12029,10 +12029,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>102653847</v>
+        <v>102651188</v>
       </c>
       <c r="B102" t="n">
-        <v>78569</v>
+        <v>98431</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12041,39 +12041,40 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562856.3529100325</v>
+        <v>562921.5566904319</v>
       </c>
       <c r="R102" t="n">
-        <v>6981718.700592224</v>
+        <v>6981622.560960029</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12116,6 +12117,11 @@
       <c r="AB102" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12142,10 +12148,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>102651188</v>
+        <v>102651045</v>
       </c>
       <c r="B103" t="n">
-        <v>98431</v>
+        <v>78569</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12154,40 +12160,39 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562921.5566904319</v>
+        <v>562932.4135675716</v>
       </c>
       <c r="R103" t="n">
-        <v>6981622.560960029</v>
+        <v>6981579.532619203</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12230,11 +12235,6 @@
       <c r="AB103" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12261,10 +12261,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>102651045</v>
+        <v>102654746</v>
       </c>
       <c r="B104" t="n">
-        <v>78569</v>
+        <v>78570</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12277,21 +12277,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12302,10 +12302,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562932.4135675716</v>
+        <v>562858.756033832</v>
       </c>
       <c r="R104" t="n">
-        <v>6981579.532619203</v>
+        <v>6981475.705113991</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12374,10 +12374,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>102654746</v>
+        <v>102655060</v>
       </c>
       <c r="B105" t="n">
-        <v>78570</v>
+        <v>57577</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12386,39 +12386,41 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>208249</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562858.756033832</v>
+        <v>562814.6747270979</v>
       </c>
       <c r="R105" t="n">
-        <v>6981475.705113991</v>
+        <v>6981374.26613691</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12487,10 +12489,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>102655060</v>
+        <v>102655085</v>
       </c>
       <c r="B106" t="n">
-        <v>57577</v>
+        <v>89673</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12499,41 +12501,39 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>208249</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562814.6747270979</v>
+        <v>562804.072420466</v>
       </c>
       <c r="R106" t="n">
-        <v>6981374.26613691</v>
+        <v>6981356.765708966</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12602,10 +12602,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>102655085</v>
+        <v>102648090</v>
       </c>
       <c r="B107" t="n">
-        <v>89673</v>
+        <v>78569</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12618,21 +12618,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>562804.072420466</v>
+        <v>563133.5384192481</v>
       </c>
       <c r="R107" t="n">
-        <v>6981356.765708966</v>
+        <v>6981078.176452862</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12715,10 +12715,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>102648090</v>
+        <v>102648761</v>
       </c>
       <c r="B108" t="n">
-        <v>78569</v>
+        <v>73631</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12727,25 +12727,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12756,10 +12756,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>563133.5384192481</v>
+        <v>563183.8939330898</v>
       </c>
       <c r="R108" t="n">
-        <v>6981078.176452862</v>
+        <v>6981043.644692466</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12828,10 +12828,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>102648761</v>
+        <v>102648428</v>
       </c>
       <c r="B109" t="n">
-        <v>73631</v>
+        <v>77506</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12840,25 +12840,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12869,10 +12869,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>563183.8939330898</v>
+        <v>563175.9462257235</v>
       </c>
       <c r="R109" t="n">
-        <v>6981043.644692466</v>
+        <v>6981124.517774746</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12941,10 +12941,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>102648428</v>
+        <v>102654177</v>
       </c>
       <c r="B110" t="n">
-        <v>77506</v>
+        <v>78603</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12953,25 +12953,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12982,10 +12982,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>563175.9462257235</v>
+        <v>562858.6316109765</v>
       </c>
       <c r="R110" t="n">
-        <v>6981124.517774746</v>
+        <v>6981647.745394537</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -13054,10 +13054,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>102654177</v>
+        <v>102653068</v>
       </c>
       <c r="B111" t="n">
-        <v>78603</v>
+        <v>96251</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13070,35 +13070,36 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562858.6316109765</v>
+        <v>562878.7966480409</v>
       </c>
       <c r="R111" t="n">
-        <v>6981647.745394537</v>
+        <v>6981854.755357474</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -13167,10 +13168,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>102653068</v>
+        <v>102653551</v>
       </c>
       <c r="B112" t="n">
-        <v>96251</v>
+        <v>78569</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13179,40 +13180,39 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>562878.7966480409</v>
+        <v>562826.8012589074</v>
       </c>
       <c r="R112" t="n">
-        <v>6981854.755357474</v>
+        <v>6981785.943111947</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13281,7 +13281,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>102653551</v>
+        <v>102653027</v>
       </c>
       <c r="B113" t="n">
         <v>78569</v>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562826.8012589074</v>
+        <v>562880.7153663491</v>
       </c>
       <c r="R113" t="n">
-        <v>6981785.943111947</v>
+        <v>6981849.786253358</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13394,10 +13394,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>102653027</v>
+        <v>102654721</v>
       </c>
       <c r="B114" t="n">
-        <v>78569</v>
+        <v>78603</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13406,25 +13406,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13435,10 +13435,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>562880.7153663491</v>
+        <v>562836.387020988</v>
       </c>
       <c r="R114" t="n">
-        <v>6981849.786253358</v>
+        <v>6981477.549958516</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13507,10 +13507,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>102654721</v>
+        <v>102655657</v>
       </c>
       <c r="B115" t="n">
-        <v>78603</v>
+        <v>95519</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13523,35 +13523,36 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>562836.387020988</v>
+        <v>562908.5115978073</v>
       </c>
       <c r="R115" t="n">
-        <v>6981477.549958516</v>
+        <v>6981235.424969721</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13620,10 +13621,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>102655657</v>
+        <v>102651021</v>
       </c>
       <c r="B116" t="n">
-        <v>95519</v>
+        <v>98520</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13636,21 +13637,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13662,10 +13663,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562908.5115978073</v>
+        <v>562936.4270200501</v>
       </c>
       <c r="R116" t="n">
-        <v>6981235.424969721</v>
+        <v>6981560.494218949</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13734,10 +13735,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>102651021</v>
+        <v>102652386</v>
       </c>
       <c r="B117" t="n">
-        <v>98520</v>
+        <v>78569</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13746,40 +13747,39 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562936.4270200501</v>
+        <v>562947.6647691409</v>
       </c>
       <c r="R117" t="n">
-        <v>6981560.494218949</v>
+        <v>6981875.652793964</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13848,10 +13848,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>102652386</v>
+        <v>102653469</v>
       </c>
       <c r="B118" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13864,21 +13864,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13889,10 +13889,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562947.6647691409</v>
+        <v>562861.7930037185</v>
       </c>
       <c r="R118" t="n">
-        <v>6981875.652793964</v>
+        <v>6981767.502632951</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13961,10 +13961,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>102653469</v>
+        <v>102654233</v>
       </c>
       <c r="B119" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13977,21 +13977,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14002,10 +14002,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>562861.7930037185</v>
+        <v>562827.9668000463</v>
       </c>
       <c r="R119" t="n">
-        <v>6981767.502632951</v>
+        <v>6981607.103229191</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -14074,7 +14074,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>102654233</v>
+        <v>102653688</v>
       </c>
       <c r="B120" t="n">
         <v>78569</v>
@@ -14115,10 +14115,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562827.9668000463</v>
+        <v>562849.5980612733</v>
       </c>
       <c r="R120" t="n">
-        <v>6981607.103229191</v>
+        <v>6981714.474385051</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14187,7 +14187,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>102653688</v>
+        <v>102650913</v>
       </c>
       <c r="B121" t="n">
         <v>78569</v>
@@ -14228,10 +14228,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562849.5980612733</v>
+        <v>563076.8062005688</v>
       </c>
       <c r="R121" t="n">
-        <v>6981714.474385051</v>
+        <v>6981442.590932302</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14300,10 +14300,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>102650913</v>
+        <v>102650575</v>
       </c>
       <c r="B122" t="n">
-        <v>78569</v>
+        <v>98431</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14312,39 +14312,40 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563076.8062005688</v>
+        <v>563135.4360743947</v>
       </c>
       <c r="R122" t="n">
-        <v>6981442.590932302</v>
+        <v>6981404.126057914</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14413,10 +14414,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>102650575</v>
+        <v>102651087</v>
       </c>
       <c r="B123" t="n">
-        <v>98431</v>
+        <v>98520</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14429,21 +14430,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14455,10 +14456,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>563135.4360743947</v>
+        <v>562913.7784049902</v>
       </c>
       <c r="R123" t="n">
-        <v>6981404.126057914</v>
+        <v>6981553.230263358</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14527,10 +14528,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>102651087</v>
+        <v>102648095</v>
       </c>
       <c r="B124" t="n">
-        <v>98520</v>
+        <v>78527</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14543,36 +14544,35 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>562913.7784049902</v>
+        <v>563133.5384192481</v>
       </c>
       <c r="R124" t="n">
-        <v>6981553.230263358</v>
+        <v>6981078.176452862</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14641,10 +14641,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>102648095</v>
+        <v>102653447</v>
       </c>
       <c r="B125" t="n">
-        <v>78527</v>
+        <v>78503</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14657,21 +14657,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14682,10 +14682,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>563133.5384192481</v>
+        <v>562859.9707017146</v>
       </c>
       <c r="R125" t="n">
-        <v>6981078.176452862</v>
+        <v>6981767.467517198</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14754,10 +14754,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>102653447</v>
+        <v>102653493</v>
       </c>
       <c r="B126" t="n">
-        <v>78503</v>
+        <v>78569</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14766,25 +14766,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14795,10 +14795,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>562859.9707017146</v>
+        <v>562859.9268687246</v>
       </c>
       <c r="R126" t="n">
-        <v>6981767.467517198</v>
+        <v>6981769.742225606</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14867,10 +14867,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>102653493</v>
+        <v>102651824</v>
       </c>
       <c r="B127" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14883,21 +14883,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14908,10 +14908,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>562859.9268687246</v>
+        <v>562963.6430342399</v>
       </c>
       <c r="R127" t="n">
-        <v>6981769.742225606</v>
+        <v>6981708.936563083</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14980,10 +14980,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>102651824</v>
+        <v>102652300</v>
       </c>
       <c r="B128" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14996,21 +14996,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15021,10 +15021,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>562963.6430342399</v>
+        <v>562959.042940647</v>
       </c>
       <c r="R128" t="n">
-        <v>6981708.936563083</v>
+        <v>6981923.657146084</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -15093,7 +15093,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>102652300</v>
+        <v>102650239</v>
       </c>
       <c r="B129" t="n">
         <v>78569</v>
@@ -15134,10 +15134,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>562959.042940647</v>
+        <v>563204.8018061253</v>
       </c>
       <c r="R129" t="n">
-        <v>6981923.657146084</v>
+        <v>6981282.117576115</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15206,7 +15206,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>102650239</v>
+        <v>102651998</v>
       </c>
       <c r="B130" t="n">
         <v>78569</v>
@@ -15247,10 +15247,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>563204.8018061253</v>
+        <v>563020.4372371376</v>
       </c>
       <c r="R130" t="n">
-        <v>6981282.117576115</v>
+        <v>6981788.76801215</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15319,10 +15319,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>102651998</v>
+        <v>102652945</v>
       </c>
       <c r="B131" t="n">
-        <v>78569</v>
+        <v>96232</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15331,39 +15331,40 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>219795</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>563020.4372371376</v>
+        <v>562882.3003695616</v>
       </c>
       <c r="R131" t="n">
-        <v>6981788.76801215</v>
+        <v>6981885.769467179</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -15432,10 +15433,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>102652945</v>
+        <v>102652856</v>
       </c>
       <c r="B132" t="n">
-        <v>96232</v>
+        <v>78533</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15448,36 +15449,35 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219795</v>
+        <v>229748</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>562882.3003695616</v>
+        <v>562880.3202819211</v>
       </c>
       <c r="R132" t="n">
-        <v>6981885.769467179</v>
+        <v>6981893.922986684</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -15546,10 +15546,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>102652856</v>
+        <v>102651142</v>
       </c>
       <c r="B133" t="n">
-        <v>78533</v>
+        <v>78569</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15558,25 +15558,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15587,10 +15587,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>562880.3202819211</v>
+        <v>562911.3593737179</v>
       </c>
       <c r="R133" t="n">
-        <v>6981893.922986684</v>
+        <v>6981584.133046838</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -15659,7 +15659,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>102651142</v>
+        <v>102654519</v>
       </c>
       <c r="B134" t="n">
         <v>78569</v>
@@ -15700,10 +15700,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>562911.3593737179</v>
+        <v>562865.9751865943</v>
       </c>
       <c r="R134" t="n">
-        <v>6981584.133046838</v>
+        <v>6981526.820768035</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -15772,7 +15772,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>102654519</v>
+        <v>102653522</v>
       </c>
       <c r="B135" t="n">
         <v>78569</v>
@@ -15813,10 +15813,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>562865.9751865943</v>
+        <v>562824.4620627351</v>
       </c>
       <c r="R135" t="n">
-        <v>6981526.820768035</v>
+        <v>6981789.083814999</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15885,10 +15885,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>102651329</v>
+        <v>102653252</v>
       </c>
       <c r="B136" t="n">
-        <v>78569</v>
+        <v>96367</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15897,39 +15897,40 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>562932.3960144327</v>
+        <v>562879.6915559154</v>
       </c>
       <c r="R136" t="n">
-        <v>6981580.442555131</v>
+        <v>6981784.686649747</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15998,7 +15999,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>102653522</v>
+        <v>102652955</v>
       </c>
       <c r="B137" t="n">
         <v>78569</v>
@@ -16039,10 +16040,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>562824.4620627351</v>
+        <v>562882.3003695616</v>
       </c>
       <c r="R137" t="n">
-        <v>6981789.083814999</v>
+        <v>6981885.769467179</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -16111,7 +16112,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>102653252</v>
+        <v>102652116</v>
       </c>
       <c r="B138" t="n">
         <v>96367</v>
@@ -16153,10 +16154,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>562879.6915559154</v>
+        <v>562972.2409195453</v>
       </c>
       <c r="R138" t="n">
-        <v>6981784.686649747</v>
+        <v>6981830.162088719</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -16225,10 +16226,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>102652955</v>
+        <v>102655856</v>
       </c>
       <c r="B139" t="n">
-        <v>78569</v>
+        <v>96334</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16237,39 +16238,40 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>562882.3003695616</v>
+        <v>562989.3318791199</v>
       </c>
       <c r="R139" t="n">
-        <v>6981885.769467179</v>
+        <v>6981157.325842476</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -16338,10 +16340,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>102652116</v>
+        <v>102649601</v>
       </c>
       <c r="B140" t="n">
-        <v>96367</v>
+        <v>96354</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16354,16 +16356,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -16380,10 +16382,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>562972.2409195453</v>
+        <v>563238.8545154623</v>
       </c>
       <c r="R140" t="n">
-        <v>6981830.162088719</v>
+        <v>6981124.370789579</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -16452,10 +16454,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>102655856</v>
+        <v>102647696</v>
       </c>
       <c r="B141" t="n">
-        <v>96334</v>
+        <v>78596</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16464,40 +16466,39 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>562989.3318791199</v>
+        <v>563079.9309635329</v>
       </c>
       <c r="R141" t="n">
-        <v>6981157.325842476</v>
+        <v>6981139.502584225</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -16566,10 +16567,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>102649601</v>
+        <v>102650361</v>
       </c>
       <c r="B142" t="n">
-        <v>96354</v>
+        <v>78569</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16578,40 +16579,39 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>563238.8545154623</v>
+        <v>563181.1473272038</v>
       </c>
       <c r="R142" t="n">
-        <v>6981124.370789579</v>
+        <v>6981326.721967046</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -16680,10 +16680,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>102647696</v>
+        <v>102650237</v>
       </c>
       <c r="B143" t="n">
-        <v>78596</v>
+        <v>78533</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16696,21 +16696,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6462</v>
+        <v>229748</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16721,10 +16721,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>563079.9309635329</v>
+        <v>563204.8018061253</v>
       </c>
       <c r="R143" t="n">
-        <v>6981139.502584225</v>
+        <v>6981282.117576115</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -16793,10 +16793,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>102650361</v>
+        <v>102650042</v>
       </c>
       <c r="B144" t="n">
-        <v>78569</v>
+        <v>78596</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16805,25 +16805,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16834,10 +16834,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>563181.1473272038</v>
+        <v>563243.519822001</v>
       </c>
       <c r="R144" t="n">
-        <v>6981326.721967046</v>
+        <v>6981236.439106781</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16906,10 +16906,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>102650237</v>
+        <v>102655087</v>
       </c>
       <c r="B145" t="n">
-        <v>78533</v>
+        <v>89356</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16922,21 +16922,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229748</v>
+        <v>5447</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16947,10 +16947,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>563204.8018061253</v>
+        <v>562804.072420466</v>
       </c>
       <c r="R145" t="n">
-        <v>6981282.117576115</v>
+        <v>6981356.765708966</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -17019,7 +17019,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>102650042</v>
+        <v>102648169</v>
       </c>
       <c r="B146" t="n">
         <v>78596</v>
@@ -17060,10 +17060,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>563243.519822001</v>
+        <v>563135.4293783343</v>
       </c>
       <c r="R146" t="n">
-        <v>6981236.439106781</v>
+        <v>6981098.242142129</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -17132,10 +17132,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>102655087</v>
+        <v>102648699</v>
       </c>
       <c r="B147" t="n">
-        <v>89356</v>
+        <v>78569</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17144,25 +17144,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17173,10 +17173,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>562804.072420466</v>
+        <v>563158.6115128727</v>
       </c>
       <c r="R147" t="n">
-        <v>6981356.765708966</v>
+        <v>6981054.535543769</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17245,10 +17245,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>102648169</v>
+        <v>102650855</v>
       </c>
       <c r="B148" t="n">
-        <v>78596</v>
+        <v>96660</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17261,35 +17261,36 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6462</v>
+        <v>219880</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>563135.4293783343</v>
+        <v>563097.9055595184</v>
       </c>
       <c r="R148" t="n">
-        <v>6981098.242142129</v>
+        <v>6981435.716405243</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -17358,10 +17359,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>102648699</v>
+        <v>102653072</v>
       </c>
       <c r="B149" t="n">
-        <v>78569</v>
+        <v>96367</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17370,39 +17371,40 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>563158.6115128727</v>
+        <v>562878.7966480409</v>
       </c>
       <c r="R149" t="n">
-        <v>6981054.535543769</v>
+        <v>6981854.755357474</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -17471,10 +17473,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>102650855</v>
+        <v>102654667</v>
       </c>
       <c r="B150" t="n">
-        <v>96660</v>
+        <v>78596</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17487,36 +17489,35 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>219880</v>
+        <v>6462</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>563097.9055595184</v>
+        <v>562842.4413773438</v>
       </c>
       <c r="R150" t="n">
-        <v>6981435.716405243</v>
+        <v>6981494.507114689</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -17585,10 +17586,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>102653072</v>
+        <v>102650004</v>
       </c>
       <c r="B151" t="n">
-        <v>96367</v>
+        <v>93044</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17601,21 +17602,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>219874</v>
+        <v>2809</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17627,10 +17628,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>562878.7966480409</v>
+        <v>563261.9341912641</v>
       </c>
       <c r="R151" t="n">
-        <v>6981854.755357474</v>
+        <v>6981203.56727221</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -17699,10 +17700,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>102654667</v>
+        <v>102647338</v>
       </c>
       <c r="B152" t="n">
-        <v>78596</v>
+        <v>78479</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17711,39 +17712,41 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6462</v>
+        <v>392</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>562842.4413773438</v>
+        <v>563053.6111565963</v>
       </c>
       <c r="R152" t="n">
-        <v>6981494.507114689</v>
+        <v>6981086.190319465</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -17794,6 +17797,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -17812,10 +17816,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>102650004</v>
+        <v>102648663</v>
       </c>
       <c r="B153" t="n">
-        <v>93044</v>
+        <v>89732</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17824,40 +17828,41 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2809</v>
+        <v>2062</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>563261.9341912641</v>
+        <v>563174.9629621522</v>
       </c>
       <c r="R153" t="n">
-        <v>6981203.56727221</v>
+        <v>6981057.583351456</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -17908,6 +17913,7 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -17926,10 +17932,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>102647338</v>
+        <v>102653984</v>
       </c>
       <c r="B154" t="n">
-        <v>78479</v>
+        <v>96332</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17938,30 +17944,31 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>392</v>
+        <v>620</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -17969,10 +17976,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>563053.6111565963</v>
+        <v>562808.2799592296</v>
       </c>
       <c r="R154" t="n">
-        <v>6981086.190319465</v>
+        <v>6981659.063998986</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -18015,6 +18022,11 @@
       <c r="AB154" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>I bergsslänt med sipperstråk. Övriga fynd i sumpskogen nedanför berget</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18042,10 +18054,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>102648663</v>
+        <v>102649112</v>
       </c>
       <c r="B155" t="n">
-        <v>89732</v>
+        <v>96332</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18054,41 +18066,44 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>563174.9629621522</v>
+        <v>563220.5012157555</v>
       </c>
       <c r="R155" t="n">
-        <v>6981057.583351456</v>
+        <v>6981083.501871014</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18139,7 +18154,6 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -18158,10 +18172,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>102653984</v>
+        <v>111223559</v>
       </c>
       <c r="B156" t="n">
-        <v>96332</v>
+        <v>78578</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18174,41 +18188,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>620</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Vålberget, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>562808.2799592296</v>
+        <v>562951.5121628437</v>
       </c>
       <c r="R156" t="n">
-        <v>6981659.063998986</v>
+        <v>6981392.834283601</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18232,7 +18242,7 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
@@ -18242,7 +18252,7 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
@@ -18252,7 +18262,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>I bergsslänt med sipperstråk. Övriga fynd i sumpskogen nedanför berget</t>
+          <t>Fertil på gammal sälg.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18261,29 +18271,32 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>102649112</v>
+        <v>111223562</v>
       </c>
       <c r="B157" t="n">
-        <v>96332</v>
+        <v>98535</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18292,47 +18305,41 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>620</v>
+        <v>222498</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Vålberget, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>563220.5012157555</v>
+        <v>562978.6324650105</v>
       </c>
       <c r="R157" t="n">
-        <v>6981083.501871014</v>
+        <v>6981546.289043762</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18356,7 +18363,7 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
@@ -18366,7 +18373,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
@@ -18386,22 +18393,26 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>102649207</v>
+        <v>111223555</v>
       </c>
       <c r="B158" t="n">
-        <v>96332</v>
+        <v>78578</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18414,43 +18425,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>620</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Vålberget, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>563219.5722406649</v>
+        <v>562908.8515312568</v>
       </c>
       <c r="R158" t="n">
-        <v>6981084.394288083</v>
+        <v>6981312.356888318</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18474,7 +18479,7 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
@@ -18484,12 +18489,17 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18504,369 +18514,15 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>111223559</v>
-      </c>
-      <c r="B159" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Vålberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q159" t="n">
-        <v>562951.5121628437</v>
-      </c>
-      <c r="R159" t="n">
-        <v>6981392.834283601</v>
-      </c>
-      <c r="S159" t="n">
-        <v>10</v>
-      </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>Håsjö</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Fertil på gammal sälg.</t>
-        </is>
-      </c>
-      <c r="AD159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT159" t="inlineStr"/>
-      <c r="AW159" t="inlineStr">
-        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX159" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>111223562</v>
-      </c>
-      <c r="B160" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>Vålberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q160" t="n">
-        <v>562978.6324650105</v>
-      </c>
-      <c r="R160" t="n">
-        <v>6981546.289043762</v>
-      </c>
-      <c r="S160" t="n">
-        <v>10</v>
-      </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>Håsjö</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT160" t="inlineStr"/>
-      <c r="AW160" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX160" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY160" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>111223555</v>
-      </c>
-      <c r="B161" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>Vålberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q161" t="n">
-        <v>562908.8515312568</v>
-      </c>
-      <c r="R161" t="n">
-        <v>6981312.356888318</v>
-      </c>
-      <c r="S161" t="n">
-        <v>10</v>
-      </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>Håsjö</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
-      <c r="AD161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT161" t="inlineStr"/>
-      <c r="AW161" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX161" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr">
+      <c r="AY158" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
